--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.0386470830697</v>
+        <v>12.03128015099883</v>
       </c>
       <c r="D2" t="n">
-        <v>26.94107965582552</v>
+        <v>4.377925444071646</v>
       </c>
       <c r="E2" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F2" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.25940304974301</v>
+        <v>9.792152995583239</v>
       </c>
       <c r="D3" t="n">
-        <v>9.839659519430381</v>
+        <v>1.598944671907437</v>
       </c>
       <c r="E3" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F3" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>67.86572309222572</v>
+        <v>11.02818000248668</v>
       </c>
       <c r="D4" t="n">
-        <v>24.791891113337</v>
+        <v>4.028682305917263</v>
       </c>
       <c r="E4" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F4" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.13747646594507</v>
+        <v>9.284839925716074</v>
       </c>
       <c r="D5" t="n">
-        <v>5.320200338542235</v>
+        <v>0.8645325550131132</v>
       </c>
       <c r="E5" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F5" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.77533557663983</v>
+        <v>9.550992031203972</v>
       </c>
       <c r="D6" t="n">
-        <v>12.97817206664986</v>
+        <v>2.108952960830603</v>
       </c>
       <c r="E6" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F6" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.26945661105405</v>
+        <v>6.218786699296283</v>
       </c>
       <c r="D7" t="n">
-        <v>22.19434645131155</v>
+        <v>3.606581298338126</v>
       </c>
       <c r="E7" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F7" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.69232543286594</v>
+        <v>6.775002882840715</v>
       </c>
       <c r="D8" t="n">
-        <v>45.20812290304955</v>
+        <v>7.346319971745552</v>
       </c>
       <c r="E8" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F8" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.28946009257135</v>
+        <v>6.059537265042845</v>
       </c>
       <c r="D9" t="n">
-        <v>42.17283639371968</v>
+        <v>6.853085913979449</v>
       </c>
       <c r="E9" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F9" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.92087551788321</v>
+        <v>5.674642271656022</v>
       </c>
       <c r="D10" t="n">
-        <v>37.13679984870409</v>
+        <v>6.034729975414415</v>
       </c>
       <c r="E10" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F10" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.35476677260377</v>
+        <v>5.582649600548113</v>
       </c>
       <c r="D11" t="n">
-        <v>34.25726332769371</v>
+        <v>5.566805290750228</v>
       </c>
       <c r="E11" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F11" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>53.91500053027337</v>
+        <v>8.761187586169424</v>
       </c>
       <c r="D12" t="n">
-        <v>48.2952478865554</v>
+        <v>7.847977781565253</v>
       </c>
       <c r="E12" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F12" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99976339335759</v>
+        <v>3.087461551420608</v>
       </c>
       <c r="D13" t="n">
-        <v>18.85415465257698</v>
+        <v>3.063800131043759</v>
       </c>
       <c r="E13" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F13" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>17.10263137648707</v>
+        <v>2.779177598679149</v>
       </c>
       <c r="D14" t="n">
-        <v>10.45628520205706</v>
+        <v>1.699146345334272</v>
       </c>
       <c r="E14" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F14" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>67.78686650399681</v>
+        <v>11.01536580689948</v>
       </c>
       <c r="D15" t="n">
-        <v>68.64133036318501</v>
+        <v>11.15421618401756</v>
       </c>
       <c r="E15" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F15" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>21.91460700081113</v>
+        <v>3.561123637631809</v>
       </c>
       <c r="D16" t="n">
-        <v>13.75597169848843</v>
+        <v>2.235345401004369</v>
       </c>
       <c r="E16" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F16" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>60.81214675199751</v>
+        <v>9.881973847199596</v>
       </c>
       <c r="D17" t="n">
-        <v>61.77600627048811</v>
+        <v>10.03860101895432</v>
       </c>
       <c r="E17" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F17" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>21.55091412662923</v>
+        <v>3.502023545577249</v>
       </c>
       <c r="D18" t="n">
-        <v>22.69687299018667</v>
+        <v>3.688241860905334</v>
       </c>
       <c r="E18" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F18" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>14.08012784032872</v>
+        <v>2.288020774053418</v>
       </c>
       <c r="D19" t="n">
-        <v>13.72953021774598</v>
+        <v>2.231048660383722</v>
       </c>
       <c r="E19" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F19" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>20.34040281034171</v>
+        <v>3.305315456680527</v>
       </c>
       <c r="D20" t="n">
-        <v>21.34693653446513</v>
+        <v>3.468877186850584</v>
       </c>
       <c r="E20" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F20" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>18.87867394321246</v>
+        <v>3.067784515772025</v>
       </c>
       <c r="D21" t="n">
-        <v>13.47573773324165</v>
+        <v>2.189807381651768</v>
       </c>
       <c r="E21" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F21" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>72.19301921928592</v>
+        <v>11.73136562313396</v>
       </c>
       <c r="D22" t="n">
-        <v>73.23306727347443</v>
+        <v>11.9003734319396</v>
       </c>
       <c r="E22" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F22" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>69.15433321896244</v>
+        <v>11.2375791480814</v>
       </c>
       <c r="D23" t="n">
-        <v>70.23852925881243</v>
+        <v>11.41376100455702</v>
       </c>
       <c r="E23" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F23" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>25.5824496167795</v>
+        <v>4.157148062726669</v>
       </c>
       <c r="D24" t="n">
-        <v>14.83391592696936</v>
+        <v>2.41051133813252</v>
       </c>
       <c r="E24" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F24" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>57.37708083657415</v>
+        <v>9.323775635943299</v>
       </c>
       <c r="D25" t="n">
-        <v>58.52694186847932</v>
+        <v>9.51062805362789</v>
       </c>
       <c r="E25" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F25" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>44.72448702186531</v>
+        <v>7.267729141053112</v>
       </c>
       <c r="D26" t="n">
-        <v>19.2687647482799</v>
+        <v>3.131174271595484</v>
       </c>
       <c r="E26" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F26" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>46.56259552286037</v>
+        <v>7.56642177246481</v>
       </c>
       <c r="D27" t="n">
-        <v>47.45104484922832</v>
+        <v>7.710794787999601</v>
       </c>
       <c r="E27" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F27" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>49.22336098774292</v>
+        <v>7.998796160508225</v>
       </c>
       <c r="D28" t="n">
-        <v>22.18490559277683</v>
+        <v>3.605047158826236</v>
       </c>
       <c r="E28" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F28" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>61.85788003881252</v>
+        <v>10.05190550630704</v>
       </c>
       <c r="D29" t="n">
-        <v>35.51168843076619</v>
+        <v>5.770649369999506</v>
       </c>
       <c r="E29" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F29" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>64.41412003427057</v>
+        <v>10.46729450556897</v>
       </c>
       <c r="D30" t="n">
-        <v>60.40458773631762</v>
+        <v>9.815745507151615</v>
       </c>
       <c r="E30" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F30" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>70.29164221461298</v>
+        <v>11.42239185987461</v>
       </c>
       <c r="D31" t="n">
-        <v>54.45832351373799</v>
+        <v>8.849477570982424</v>
       </c>
       <c r="E31" t="n">
-        <v>19.18361784468398</v>
+        <v>3.117337899761147</v>
       </c>
       <c r="F31" t="n">
-        <v>20.23815124335113</v>
+        <v>3.288699577044558</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
